--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T14:16:19+00:00</t>
+    <t>2025-02-13T08:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:25:30+00:00</t>
+    <t>2025-02-13T08:54:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:54:32+00:00</t>
+    <t>2025-02-14T08:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T08:32:04+00:00</t>
+    <t>2025-02-14T09:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -908,7 +908,7 @@
     <t>The kind or type of device.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-medicaldevices</t>
+    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-medicaldevice</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1503,7 +1503,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="42.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.37109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="76.08203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:49:00+00:00</t>
+    <t>2025-02-17T15:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T15:20:00+00:00</t>
+    <t>2025-02-18T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T09:36:51+00:00</t>
+    <t>2025-02-21T10:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -908,7 +908,7 @@
     <t>The kind or type of device.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-medicaldevice</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medicaldevices</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1503,7 +1503,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="42.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="76.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.37109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
